--- a/docs/sba_loans_dictionary.xlsx
+++ b/docs/sba_loans_dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edu/Desktop/Google DA Capstone/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edu/Desktop/Git/Small-Business-Credit-Risk/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D659EF7-B6FC-B14E-91A8-5517907DD84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40AB29D-77A4-C643-9F12-6FB90E58FBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sba_loans" sheetId="4" r:id="rId1"/>
@@ -1971,18 +1971,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Notes xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d" xsi:nil="true"/>
-    <DateofEmail xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EAAD665B16F65A4E9B725FF1EAA99F85" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c08b791da64872a0b043fc7d9a906513">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="25a9b3fa-830d-4178-97f6-f511dad11a7d" xmlns:ns3="ba6df21a-8891-4f1c-9884-d3b7c557017b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="84e6bade16f8745f6fd058c20afab5bc" ns2:_="" ns3:_="">
     <xsd:import namespace="25a9b3fa-830d-4178-97f6-f511dad11a7d"/>
@@ -2219,6 +2207,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Notes xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d" xsi:nil="true"/>
+    <DateofEmail xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="25a9b3fa-830d-4178-97f6-f511dad11a7d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2229,16 +2229,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F90F8B6-573D-4518-B8F1-5AB240F99466}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="25a9b3fa-830d-4178-97f6-f511dad11a7d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B31D71FB-A781-48C8-88C5-C417D0816AAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2257,6 +2247,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F90F8B6-573D-4518-B8F1-5AB240F99466}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="25a9b3fa-830d-4178-97f6-f511dad11a7d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C6E5C8-069E-4794-97F1-A3A51E06B056}">
   <ds:schemaRefs>
